--- a/research/traditional_assets/database/data/saint_lucia/saint_lucia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/saint_lucia/saint_lucia_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,41 +587,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0911</v>
+      </c>
+      <c r="E2">
+        <v>0.0857</v>
+      </c>
       <c r="G2">
-        <v>-0.9785407725321887</v>
+        <v>0.3964852121731676</v>
       </c>
       <c r="H2">
-        <v>-0.9785407725321887</v>
+        <v>0.3964852121731676</v>
       </c>
       <c r="I2">
-        <v>0.7752503576537911</v>
+        <v>0.9304972138876982</v>
       </c>
       <c r="J2">
-        <v>0.7721369024021695</v>
+        <v>0.9304972138876982</v>
       </c>
       <c r="K2">
-        <v>4.348</v>
+        <v>40.254</v>
       </c>
       <c r="L2">
-        <v>0.6220314735336194</v>
+        <v>0.8627089584226318</v>
       </c>
       <c r="M2">
-        <v>0.985</v>
+        <v>0.975</v>
       </c>
       <c r="N2">
-        <v>0.01204892966360856</v>
+        <v>0.00707341845618108</v>
       </c>
       <c r="O2">
-        <v>0.2265409383624655</v>
+        <v>0.02422119540915188</v>
       </c>
       <c r="P2">
-        <v>0.985</v>
+        <v>0.975</v>
       </c>
       <c r="Q2">
-        <v>0.01204892966360856</v>
+        <v>0.00707341845618108</v>
       </c>
       <c r="R2">
-        <v>0.2265409383624655</v>
+        <v>0.02422119540915188</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.374</v>
+        <v>2.112</v>
       </c>
       <c r="V2">
-        <v>0.02903975535168196</v>
+        <v>0.01532211259431225</v>
       </c>
       <c r="W2">
-        <v>0.08097346295323174</v>
+        <v>0.05150943396226416</v>
       </c>
       <c r="X2">
-        <v>0.1182330865537008</v>
+        <v>0.1645062494821759</v>
       </c>
       <c r="Y2">
-        <v>-0.03725962360046904</v>
+        <v>-0.1129968155199117</v>
       </c>
       <c r="Z2">
-        <v>0.07482177645522467</v>
+        <v>0.27561520195636</v>
       </c>
       <c r="AA2">
-        <v>0.06675646244282898</v>
+        <v>0.05551780375101929</v>
       </c>
       <c r="AB2">
-        <v>0.1024406013556202</v>
+        <v>0.1471087040049937</v>
       </c>
       <c r="AC2">
-        <v>-0.03568413891279122</v>
+        <v>-0.09159090025397444</v>
       </c>
       <c r="AD2">
-        <v>27.33</v>
+        <v>36.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>27.33</v>
+        <v>36.9</v>
       </c>
       <c r="AG2">
-        <v>24.956</v>
+        <v>34.788</v>
       </c>
       <c r="AH2">
-        <v>0.2505500550055005</v>
+        <v>0.2111708824539315</v>
       </c>
       <c r="AI2">
-        <v>0.2088970419628526</v>
+        <v>0.1833996023856859</v>
       </c>
       <c r="AJ2">
-        <v>0.2338762581298146</v>
+        <v>0.2015200315128484</v>
       </c>
       <c r="AK2">
-        <v>0.1942766394718814</v>
+        <v>0.1747367998071204</v>
       </c>
       <c r="AL2">
-        <v>1.442</v>
+        <v>2.26</v>
       </c>
       <c r="AM2">
-        <v>1.442</v>
+        <v>2.26</v>
       </c>
       <c r="AN2">
-        <v>5.980306345733041</v>
+        <v>0.8891566265060241</v>
       </c>
       <c r="AO2">
-        <v>3.757975034674064</v>
+        <v>19.21106194690266</v>
       </c>
       <c r="AP2">
-        <v>5.460831509846827</v>
+        <v>0.8382650602409638</v>
       </c>
       <c r="AQ2">
-        <v>3.757975034674064</v>
+        <v>19.21106194690266</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sterling Investments Limited (JMSE:SIL)</t>
+          <t>Mayberry Jamaican Equities Limited (JMSE:MJE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4243119266055046</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.4243119266055046</v>
       </c>
       <c r="I3">
-        <v>0.757258064516129</v>
+        <v>0.9495412844036697</v>
       </c>
       <c r="J3">
-        <v>0.75117567042363</v>
+        <v>0.9495412844036697</v>
       </c>
       <c r="K3">
-        <v>0.988</v>
+        <v>39.1</v>
       </c>
       <c r="L3">
-        <v>0.7967741935483871</v>
+        <v>0.8967889908256881</v>
       </c>
       <c r="M3">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="N3">
-        <v>0.06352941176470588</v>
+        <v>0.004509803921568628</v>
       </c>
       <c r="O3">
-        <v>0.4919028340080971</v>
+        <v>0.01235294117647059</v>
       </c>
       <c r="P3">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="Q3">
-        <v>0.06352941176470588</v>
+        <v>0.004509803921568628</v>
       </c>
       <c r="R3">
-        <v>0.4919028340080971</v>
+        <v>0.01235294117647059</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,67 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.044</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>0.005751633986928104</v>
+        <v>0.01960784313725491</v>
       </c>
       <c r="W3">
-        <v>0.1142196531791907</v>
+        <v>0.4199785177228786</v>
       </c>
       <c r="X3">
-        <v>0.1249411357512203</v>
+        <v>0.1528934307046437</v>
       </c>
       <c r="Y3">
-        <v>-0.01072148257202951</v>
+        <v>0.267085087018235</v>
       </c>
       <c r="Z3">
-        <v>0.1046236922038474</v>
+        <v>0.3825568131964552</v>
       </c>
       <c r="AA3">
-        <v>0.07859077213342061</v>
+        <v>0.3632534877599368</v>
       </c>
       <c r="AB3">
-        <v>0.1042376340552201</v>
+        <v>0.1434609096773576</v>
       </c>
       <c r="AC3">
-        <v>-0.0256468619217995</v>
+        <v>0.2197925780825792</v>
       </c>
       <c r="AD3">
-        <v>4.13</v>
+        <v>24.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.13</v>
+        <v>24.8</v>
       </c>
       <c r="AG3">
-        <v>4.086</v>
+        <v>22.7</v>
       </c>
       <c r="AH3">
-        <v>0.3505942275042445</v>
+        <v>0.1880212282031842</v>
       </c>
       <c r="AI3">
-        <v>0.284239504473503</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AJ3">
-        <v>0.348159509202454</v>
+        <v>0.174884437596302</v>
       </c>
       <c r="AK3">
-        <v>0.2820654424962032</v>
+        <v>0.1547375596455351</v>
       </c>
       <c r="AL3">
-        <v>0.212</v>
+        <v>1.68</v>
       </c>
       <c r="AM3">
-        <v>0.212</v>
+        <v>1.68</v>
+      </c>
+      <c r="AN3">
+        <v>0.5975903614457831</v>
       </c>
       <c r="AO3">
-        <v>4.429245283018868</v>
+        <v>24.64285714285714</v>
+      </c>
+      <c r="AP3">
+        <v>0.5469879518072289</v>
       </c>
       <c r="AQ3">
-        <v>4.429245283018868</v>
+        <v>24.64285714285714</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mayberry Jamaican Equities Limited (JMSE:MJE)</t>
+          <t>Sterling Investments Limited (JMSE:SIL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,41 +849,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.0911</v>
+      </c>
+      <c r="E4">
+        <v>0.0857</v>
+      </c>
       <c r="G4">
-        <v>-1.189565217391304</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>-1.189565217391304</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.7791304347826088</v>
+        <v>0.7294642857142856</v>
       </c>
       <c r="J4">
-        <v>0.7791304347826088</v>
+        <v>0.7294642857142856</v>
       </c>
       <c r="K4">
-        <v>3.36</v>
+        <v>0.546</v>
       </c>
       <c r="L4">
-        <v>0.5843478260869565</v>
+        <v>0.4875</v>
       </c>
       <c r="M4">
-        <v>0.499</v>
+        <v>0.492</v>
       </c>
       <c r="N4">
-        <v>0.006734143049932524</v>
+        <v>0.05970873786407767</v>
       </c>
       <c r="O4">
-        <v>0.1485119047619048</v>
+        <v>0.901098901098901</v>
       </c>
       <c r="P4">
-        <v>0.499</v>
+        <v>0.492</v>
       </c>
       <c r="Q4">
-        <v>0.006734143049932524</v>
+        <v>0.05970873786407767</v>
       </c>
       <c r="R4">
-        <v>0.1485119047619048</v>
+        <v>0.901098901098901</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,73 +898,186 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.33</v>
+        <v>0.01</v>
       </c>
       <c r="V4">
-        <v>0.03144399460188934</v>
+        <v>0.001213592233009709</v>
       </c>
       <c r="W4">
-        <v>0.04772727272727272</v>
+        <v>0.05150943396226416</v>
       </c>
       <c r="X4">
-        <v>0.1115250373561813</v>
+        <v>0.1645062494821759</v>
       </c>
       <c r="Y4">
-        <v>-0.06379776462890857</v>
+        <v>-0.1129968155199117</v>
       </c>
       <c r="Z4">
-        <v>0.0704916023047689</v>
+        <v>0.07610763794509377</v>
       </c>
       <c r="AA4">
-        <v>0.05492215275223734</v>
+        <v>0.05551780375101929</v>
       </c>
       <c r="AB4">
-        <v>0.1006435686560203</v>
+        <v>0.1471087040049937</v>
       </c>
       <c r="AC4">
-        <v>-0.04572141590378294</v>
+        <v>-0.09159090025397444</v>
       </c>
       <c r="AD4">
-        <v>23.2</v>
+        <v>3.23</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>23.2</v>
+        <v>3.23</v>
       </c>
       <c r="AG4">
-        <v>20.87</v>
+        <v>3.22</v>
       </c>
       <c r="AH4">
-        <v>0.2384378211716341</v>
+        <v>0.2816041848299913</v>
       </c>
       <c r="AI4">
-        <v>0.1994840928632846</v>
+        <v>0.2955169258920403</v>
       </c>
       <c r="AJ4">
-        <v>0.2197536064020217</v>
+        <v>0.2809773123909249</v>
       </c>
       <c r="AK4">
-        <v>0.1831183644818812</v>
+        <v>0.2948717948717949</v>
       </c>
       <c r="AL4">
-        <v>1.23</v>
+        <v>0.257</v>
       </c>
       <c r="AM4">
-        <v>1.23</v>
-      </c>
-      <c r="AN4">
-        <v>5.076586433260394</v>
+        <v>0.257</v>
       </c>
       <c r="AO4">
-        <v>3.642276422764228</v>
-      </c>
-      <c r="AP4">
-        <v>4.566739606126914</v>
+        <v>3.178988326848249</v>
       </c>
       <c r="AQ4">
-        <v>3.642276422764228</v>
+        <v>3.178988326848249</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Saint Lucia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Portland JSX Limited (JMSE:PJX)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0.6185567010309279</v>
+      </c>
+      <c r="J5">
+        <v>0.6185567010309279</v>
+      </c>
+      <c r="K5">
+        <v>0.608</v>
+      </c>
+      <c r="L5">
+        <v>0.3134020618556701</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.002</v>
+      </c>
+      <c r="V5">
+        <v>8.888888888888889e-05</v>
+      </c>
+      <c r="W5">
+        <v>0.01911949685534591</v>
+      </c>
+      <c r="X5">
+        <v>0.1646678080937995</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1455483112384535</v>
+      </c>
+      <c r="Z5">
+        <v>0.04777383766745469</v>
+      </c>
+      <c r="AA5">
+        <v>0.02955082742316785</v>
+      </c>
+      <c r="AB5">
+        <v>0.1471535316713991</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1176027042482312</v>
+      </c>
+      <c r="AD5">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AG5">
+        <v>8.867999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.2827542237806822</v>
+      </c>
+      <c r="AI5">
+        <v>0.2138895587171449</v>
+      </c>
+      <c r="AJ5">
+        <v>0.282708492731446</v>
+      </c>
+      <c r="AK5">
+        <v>0.2138516446416514</v>
+      </c>
+      <c r="AL5">
+        <v>0.323</v>
+      </c>
+      <c r="AM5">
+        <v>0.323</v>
+      </c>
+      <c r="AO5">
+        <v>3.715170278637771</v>
+      </c>
+      <c r="AQ5">
+        <v>3.715170278637771</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saint_lucia/saint_lucia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/saint_lucia/saint_lucia_investments_asset_management.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0911</v>
+        <v>0.0834</v>
       </c>
       <c r="E2">
-        <v>0.0857</v>
+        <v>0.0254</v>
       </c>
       <c r="G2">
-        <v>0.3964852121731676</v>
+        <v>38.1004366812227</v>
       </c>
       <c r="H2">
-        <v>0.3964852121731676</v>
+        <v>38.1004366812227</v>
       </c>
       <c r="I2">
-        <v>0.9304972138876982</v>
+        <v>-15.12117903930131</v>
       </c>
       <c r="J2">
-        <v>0.9304972138876982</v>
+        <v>-15.12117903930131</v>
       </c>
       <c r="K2">
-        <v>40.254</v>
+        <v>-17.044</v>
       </c>
       <c r="L2">
-        <v>0.8627089584226318</v>
+        <v>-18.60698689956332</v>
       </c>
       <c r="M2">
-        <v>0.975</v>
+        <v>0.9430000000000001</v>
       </c>
       <c r="N2">
-        <v>0.00707341845618108</v>
+        <v>0.008944323247652472</v>
       </c>
       <c r="O2">
-        <v>0.02422119540915188</v>
+        <v>-0.05532738793710397</v>
       </c>
       <c r="P2">
-        <v>0.975</v>
+        <v>0.9430000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.00707341845618108</v>
+        <v>0.008944323247652472</v>
       </c>
       <c r="R2">
-        <v>0.02422119540915188</v>
+        <v>-0.05532738793710397</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.112</v>
+        <v>4.784</v>
       </c>
       <c r="V2">
-        <v>0.01532211259431225</v>
+        <v>0.04537607891491986</v>
       </c>
       <c r="W2">
-        <v>0.05150943396226416</v>
+        <v>-0.0625</v>
       </c>
       <c r="X2">
-        <v>0.1645062494821759</v>
+        <v>0.1922476739337491</v>
       </c>
       <c r="Y2">
-        <v>-0.1129968155199117</v>
+        <v>-0.2547476739337491</v>
       </c>
       <c r="Z2">
-        <v>0.27561520195636</v>
+        <v>0.004600980470947521</v>
       </c>
       <c r="AA2">
-        <v>0.05551780375101929</v>
+        <v>-0.03435582822085889</v>
       </c>
       <c r="AB2">
-        <v>0.1471087040049937</v>
+        <v>0.1689083732797599</v>
       </c>
       <c r="AC2">
-        <v>-0.09159090025397444</v>
+        <v>-0.2087438340325417</v>
       </c>
       <c r="AD2">
-        <v>36.9</v>
+        <v>51.04</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>36.9</v>
+        <v>51.04</v>
       </c>
       <c r="AG2">
-        <v>34.788</v>
+        <v>46.256</v>
       </c>
       <c r="AH2">
-        <v>0.2111708824539315</v>
+        <v>0.3261967150252444</v>
       </c>
       <c r="AI2">
-        <v>0.1833996023856859</v>
+        <v>0.2602620978022538</v>
       </c>
       <c r="AJ2">
-        <v>0.2015200315128484</v>
+        <v>0.3049457431799903</v>
       </c>
       <c r="AK2">
-        <v>0.1747367998071204</v>
+        <v>0.2417653638292757</v>
       </c>
       <c r="AL2">
-        <v>2.26</v>
+        <v>3.329</v>
       </c>
       <c r="AM2">
-        <v>2.26</v>
+        <v>3.329</v>
       </c>
       <c r="AN2">
-        <v>0.8891566265060241</v>
+        <v>-10.08695652173913</v>
       </c>
       <c r="AO2">
-        <v>19.21106194690266</v>
+        <v>-4.160708921598077</v>
       </c>
       <c r="AP2">
-        <v>0.8382650602409638</v>
+        <v>-9.141501976284585</v>
       </c>
       <c r="AQ2">
-        <v>19.21106194690266</v>
+        <v>-4.160708921598077</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mayberry Jamaican Equities Limited (JMSE:MJE)</t>
+          <t>Sterling Investments Limited (JMSE:SIL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,41 +721,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0834</v>
+      </c>
+      <c r="E3">
+        <v>0.0254</v>
+      </c>
       <c r="G3">
-        <v>0.4243119266055046</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.4243119266055046</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9495412844036697</v>
+        <v>0.6866812227074236</v>
       </c>
       <c r="J3">
-        <v>0.9495412844036697</v>
+        <v>0.6866812227074236</v>
       </c>
       <c r="K3">
-        <v>39.1</v>
+        <v>0.606</v>
       </c>
       <c r="L3">
-        <v>0.8967889908256881</v>
+        <v>0.6615720524017467</v>
       </c>
       <c r="M3">
-        <v>0.483</v>
+        <v>0.393</v>
       </c>
       <c r="N3">
-        <v>0.004509803921568628</v>
+        <v>0.05511921458625526</v>
       </c>
       <c r="O3">
-        <v>0.01235294117647059</v>
+        <v>0.6485148514851485</v>
       </c>
       <c r="P3">
-        <v>0.483</v>
+        <v>0.393</v>
       </c>
       <c r="Q3">
-        <v>0.004509803921568628</v>
+        <v>0.05511921458625526</v>
       </c>
       <c r="R3">
-        <v>0.01235294117647059</v>
+        <v>0.6485148514851485</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +770,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>0.004</v>
       </c>
       <c r="V3">
-        <v>0.01960784313725491</v>
+        <v>0.0005610098176718093</v>
       </c>
       <c r="W3">
-        <v>0.4199785177228786</v>
+        <v>0.0787012987012987</v>
       </c>
       <c r="X3">
-        <v>0.1528934307046437</v>
+        <v>0.1922476739337491</v>
       </c>
       <c r="Y3">
-        <v>0.267085087018235</v>
+        <v>-0.1135463752324504</v>
       </c>
       <c r="Z3">
-        <v>0.3825568131964552</v>
+        <v>0.08388278388278389</v>
       </c>
       <c r="AA3">
-        <v>0.3632534877599368</v>
+        <v>0.0576007326007326</v>
       </c>
       <c r="AB3">
-        <v>0.1434609096773576</v>
+        <v>0.1689083732797599</v>
       </c>
       <c r="AC3">
-        <v>0.2197925780825792</v>
+        <v>-0.1113076406790273</v>
       </c>
       <c r="AD3">
-        <v>24.8</v>
+        <v>2.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>24.8</v>
+        <v>2.8</v>
       </c>
       <c r="AG3">
-        <v>22.7</v>
+        <v>2.796</v>
       </c>
       <c r="AH3">
-        <v>0.1880212282031842</v>
+        <v>0.2819738167170191</v>
       </c>
       <c r="AI3">
-        <v>0.1666666666666667</v>
+        <v>0.2599814298978644</v>
       </c>
       <c r="AJ3">
-        <v>0.174884437596302</v>
+        <v>0.2816844650413056</v>
       </c>
       <c r="AK3">
-        <v>0.1547375596455351</v>
+        <v>0.2597064833735835</v>
       </c>
       <c r="AL3">
-        <v>1.68</v>
+        <v>0.175</v>
       </c>
       <c r="AM3">
-        <v>1.68</v>
-      </c>
-      <c r="AN3">
-        <v>0.5975903614457831</v>
+        <v>0.175</v>
       </c>
       <c r="AO3">
-        <v>24.64285714285714</v>
-      </c>
-      <c r="AP3">
-        <v>0.5469879518072289</v>
+        <v>3.594285714285715</v>
       </c>
       <c r="AQ3">
-        <v>24.64285714285714</v>
+        <v>3.594285714285715</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sterling Investments Limited (JMSE:SIL)</t>
+          <t>Mayberry Jamaican Equities Limited (JMSE:MJE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,47 +849,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0911</v>
-      </c>
-      <c r="E4">
-        <v>0.0857</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0.7294642857142856</v>
-      </c>
-      <c r="J4">
-        <v>0.7294642857142856</v>
-      </c>
       <c r="K4">
-        <v>0.546</v>
-      </c>
-      <c r="L4">
-        <v>0.4875</v>
+        <v>-7.75</v>
       </c>
       <c r="M4">
-        <v>0.492</v>
+        <v>0.55</v>
       </c>
       <c r="N4">
-        <v>0.05970873786407767</v>
+        <v>0.007161458333333334</v>
       </c>
       <c r="O4">
-        <v>0.901098901098901</v>
+        <v>-0.07096774193548387</v>
       </c>
       <c r="P4">
-        <v>0.492</v>
+        <v>0.55</v>
       </c>
       <c r="Q4">
-        <v>0.05970873786407767</v>
+        <v>0.007161458333333334</v>
       </c>
       <c r="R4">
-        <v>0.901098901098901</v>
+        <v>-0.07096774193548387</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,67 +877,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.01</v>
+        <v>1.38</v>
       </c>
       <c r="V4">
-        <v>0.001213592233009709</v>
+        <v>0.01796875</v>
       </c>
       <c r="W4">
-        <v>0.05150943396226416</v>
+        <v>-0.0625</v>
       </c>
       <c r="X4">
-        <v>0.1645062494821759</v>
+        <v>0.2083477590886414</v>
       </c>
       <c r="Y4">
-        <v>-0.1129968155199117</v>
+        <v>-0.2708477590886414</v>
       </c>
       <c r="Z4">
-        <v>0.07610763794509377</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.05551780375101929</v>
+        <v>-0.03435582822085889</v>
       </c>
       <c r="AB4">
-        <v>0.1471087040049937</v>
+        <v>0.1743880058116828</v>
       </c>
       <c r="AC4">
-        <v>-0.09159090025397444</v>
+        <v>-0.2087438340325417</v>
       </c>
       <c r="AD4">
-        <v>3.23</v>
+        <v>44.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.23</v>
+        <v>44.4</v>
       </c>
       <c r="AG4">
-        <v>3.22</v>
+        <v>43.02</v>
       </c>
       <c r="AH4">
-        <v>0.2816041848299913</v>
+        <v>0.3663366336633664</v>
       </c>
       <c r="AI4">
-        <v>0.2955169258920403</v>
+        <v>0.2794210195091252</v>
       </c>
       <c r="AJ4">
-        <v>0.2809773123909249</v>
+        <v>0.3590385578367551</v>
       </c>
       <c r="AK4">
-        <v>0.2948717948717949</v>
+        <v>0.2731081767394616</v>
       </c>
       <c r="AL4">
-        <v>0.257</v>
+        <v>2.69</v>
       </c>
       <c r="AM4">
-        <v>0.257</v>
+        <v>2.69</v>
+      </c>
+      <c r="AN4">
+        <v>-8.774703557312254</v>
       </c>
       <c r="AO4">
-        <v>3.178988326848249</v>
+        <v>-1.87360594795539</v>
+      </c>
+      <c r="AP4">
+        <v>-8.50197628458498</v>
       </c>
       <c r="AQ4">
-        <v>3.178988326848249</v>
+        <v>-1.87360594795539</v>
       </c>
     </row>
     <row r="5">
@@ -977,23 +962,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0.6185567010309279</v>
-      </c>
-      <c r="J5">
-        <v>0.6185567010309279</v>
-      </c>
       <c r="K5">
-        <v>0.608</v>
-      </c>
-      <c r="L5">
-        <v>0.3134020618556701</v>
+        <v>-9.9</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,7 +972,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1011,73 +981,73 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.002</v>
+        <v>3.4</v>
       </c>
       <c r="V5">
-        <v>8.888888888888889e-05</v>
+        <v>0.1581395348837209</v>
       </c>
       <c r="W5">
-        <v>0.01911949685534591</v>
+        <v>-0.303680981595092</v>
       </c>
       <c r="X5">
-        <v>0.1646678080937995</v>
+        <v>0.173656913486769</v>
       </c>
       <c r="Y5">
-        <v>-0.1455483112384535</v>
+        <v>-0.4773378950818611</v>
       </c>
       <c r="Z5">
-        <v>0.04777383766745469</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>0.02955082742316785</v>
+        <v>-0.2276454133307611</v>
       </c>
       <c r="AB5">
-        <v>0.1471535316713991</v>
+        <v>0.1648661165757624</v>
       </c>
       <c r="AC5">
-        <v>-0.1176027042482312</v>
+        <v>-0.3925115299065235</v>
       </c>
       <c r="AD5">
-        <v>8.869999999999999</v>
+        <v>3.84</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8.869999999999999</v>
+        <v>3.84</v>
       </c>
       <c r="AG5">
-        <v>8.867999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.2827542237806822</v>
+        <v>0.1515390686661405</v>
       </c>
       <c r="AI5">
-        <v>0.2138895587171449</v>
+        <v>0.1452344931921331</v>
       </c>
       <c r="AJ5">
-        <v>0.282708492731446</v>
+        <v>0.02005469462169553</v>
       </c>
       <c r="AK5">
-        <v>0.2138516446416514</v>
+        <v>0.01909722222222222</v>
       </c>
       <c r="AL5">
-        <v>0.323</v>
+        <v>0.464</v>
       </c>
       <c r="AM5">
-        <v>0.323</v>
+        <v>0.464</v>
       </c>
       <c r="AO5">
-        <v>3.715170278637771</v>
+        <v>-20.34482758620689</v>
       </c>
       <c r="AQ5">
-        <v>3.715170278637771</v>
+        <v>-20.34482758620689</v>
       </c>
     </row>
   </sheetData>
